--- a/artfynd/A 18318-2026 artfynd.xlsx
+++ b/artfynd/A 18318-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132902404</v>
       </c>
       <c r="B2" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18318-2026 artfynd.xlsx
+++ b/artfynd/A 18318-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132902404</v>
+        <v>132902385</v>
       </c>
       <c r="B2" t="n">
-        <v>98005</v>
+        <v>58658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -730,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597197</v>
+        <v>597300</v>
       </c>
       <c r="R2" t="n">
-        <v>6372260</v>
+        <v>6372208</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -784,7 +780,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -806,7 +801,7 @@
         <v>132902436</v>
       </c>
       <c r="B3" t="n">
-        <v>8444</v>
+        <v>8449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132902385</v>
+        <v>133406927</v>
       </c>
       <c r="B4" t="n">
-        <v>58641</v>
+        <v>8449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,38 +927,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597300</v>
+        <v>597226</v>
       </c>
       <c r="R4" t="n">
-        <v>6372208</v>
+        <v>6372218</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,6 +1018,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1041,6 +1034,134 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132902404</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kråkelund, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>597197</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6372260</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18318-2026 artfynd.xlsx
+++ b/artfynd/A 18318-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132902385</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132902436</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133406927</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1162,8 +1182,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132902404</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>